--- a/artfynd/A 60940-2025 artfynd.xlsx
+++ b/artfynd/A 60940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1552914</v>
+        <v>292954</v>
       </c>
       <c r="B2" t="n">
-        <v>89411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567136.7446983467</v>
+        <v>567136</v>
       </c>
       <c r="R2" t="n">
-        <v>6738817.345512079</v>
+        <v>6738810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,14 @@
           <t>2009-05-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-05-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>rikligt på 1 högstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +772,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # 200-årig tall</t>
+          <t>1 substratenheter # vitrötad ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>292954</v>
+        <v>1552914</v>
       </c>
       <c r="B3" t="n">
-        <v>79432</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567135.9131128521</v>
+        <v>567137</v>
       </c>
       <c r="R3" t="n">
-        <v>6738809.512929892</v>
+        <v>6738817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,24 +862,9 @@
           <t>2009-05-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-05-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt på 1 högstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +886,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # vitrötad ved på gammal tallhögstubbe</t>
+          <t>1 substratenheter # 200-årig tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,15 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116650904</v>
+        <v>116650898</v>
       </c>
       <c r="B4" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566685</v>
+        <v>566734</v>
       </c>
       <c r="R4" t="n">
-        <v>6739413</v>
+        <v>6739253</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1018,27 +983,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid vägkanten</t>
+          <t>vid vägkanten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,6 +1027,128 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116650904</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ångelfäbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566685</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6739413</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vid vägkanten</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60940-2025 artfynd.xlsx
+++ b/artfynd/A 60940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
           <t>Biol. inventering inför vindkraftsutbyggnad</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/292954</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
           <t>Biol. inventering inför vindkraftsutbyggnad</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1552914</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116650898</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,8 +1169,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116650904</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>